--- a/output/full_scan/batch_seq1_2026-06-30.xlsx
+++ b/output/full_scan/batch_seq1_2026-06-30.xlsx
@@ -527,21 +527,21 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>1447</v>
+        <v>1560</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>力鵬</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>765.9814095834264</v>
+        <v>1035.052076781086</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>7.52</v>
+        <v>762</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -552,29 +552,29 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>75.60704982253112</v>
+        <v>61.88286464474763</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>28.40408783205057</v>
+        <v>23.45611991836366</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>1.514055376340812</v>
+        <v>1.390342409615122</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.0663499463358552</v>
+        <v>3.424931039437986</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, hist_turn_positive, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>763.4586603005322</v>
+        <v>978.4586603005322</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>55.5</v>
@@ -605,16 +605,16 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>60.58813793997332</v>
+        <v>60.58813779219062</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>32.25566670154579</v>
+        <v>32.25566677583014</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>0.385263375375465</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0</v>
@@ -623,31 +623,31 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>-0.0030269498213945</v>
+        <v>-0.0030269496115198</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>1444</v>
+        <v>1314</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>力麗</t>
+          <t>中石化</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>730.4437456310834</v>
+        <v>970.042017123259</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>8.960000000000001</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,16 +658,16 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>81.52817802543304</v>
+        <v>64.58314689762724</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>34.40949419995332</v>
+        <v>20.50035369215031</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>3.644374563108341</v>
+        <v>1.149088190935659</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>0</v>
@@ -676,31 +676,31 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.1381568190993738</v>
+        <v>0.0336184992280042</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>1434</v>
+        <v>1447</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>福懋</t>
+          <t>力鵬</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>724.9291310402606</v>
+        <v>965.9814095834264</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>16.95</v>
+        <v>7.52</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,13 +711,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>57.33615574863033</v>
+        <v>75.60704982615749</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>23.24349218031693</v>
+        <v>28.40408786240804</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.3855955887401287</v>
+        <v>1.514055376340812</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.014600005638409</v>
+        <v>0.0663499463358552</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>1525</v>
+        <v>1444</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>江申</t>
+          <t>力麗</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>720.3272679771812</v>
+        <v>930.4437456310834</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>67.40000000000001</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>57.62246882667858</v>
+        <v>81.52817803453615</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>24.67127506413556</v>
+        <v>34.40949416180955</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>4.141662277052739</v>
+        <v>3.644374563108341</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-0.3073357615652964</v>
+        <v>0.1381568190955586</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>1560</v>
+        <v>1515</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>力山</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>720.0520767810856</v>
+        <v>905.0038312212528</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>762</v>
+        <v>32.25</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,16 +817,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>61.88286463000071</v>
+        <v>79.77921731831859</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>23.4561199339417</v>
+        <v>39.54517636775734</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1.390342409615122</v>
+        <v>1.600383122125269</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>3.424931040296428</v>
+        <v>0.7901918088004549</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>1503</v>
+        <v>1301</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>706.4019293311071</v>
+        <v>884.1048278828669</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>239.5</v>
+        <v>54.5</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>56.9659269320473</v>
+        <v>58.97185869507301</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>20.22331363676109</v>
+        <v>23.10541422898431</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.260821056043752</v>
+        <v>0.7104827882866828</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>-0.620051946929209</v>
+        <v>0.7238091007049654</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>1515</v>
+        <v>1525</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>力山</t>
+          <t>江申</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>705.0038312212527</v>
+        <v>880.3272679771812</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>32.25</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,16 +923,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>79.77921729888318</v>
+        <v>57.62246881403952</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>39.54517630444967</v>
+        <v>24.67127504954775</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1.600383122125269</v>
+        <v>4.141662277052739</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.7901918088004549</v>
+        <v>-0.3073357615271272</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>1314</v>
+        <v>1434</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>中石化</t>
+          <t>福懋</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>680.0420171232591</v>
+        <v>854.9291310402606</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>8.359999999999999</v>
+        <v>16.95</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,13 +976,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>64.58314695882702</v>
+        <v>57.33615557906489</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>20.50035368281928</v>
+        <v>23.24349218677986</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1.149088190935659</v>
+        <v>0.3855955887401287</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.0336184992032009</v>
+        <v>0.0146000057051901</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>1301</v>
+        <v>1229</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>聯華</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>664.1048278828669</v>
+        <v>851.2969577158462</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>54.5</v>
+        <v>42.95</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,13 +1029,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>58.97185873671076</v>
+        <v>58.49690040594203</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>23.1054142541009</v>
+        <v>24.31493739158461</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.7104827882866828</v>
+        <v>0.6374510049911817</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.7238091006095679</v>
+        <v>0.1345505475056522</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>1312</v>
+        <v>1503</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>國喬</t>
+          <t>士電</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>649.7475156381042</v>
+        <v>821.4019293311071</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>14.1</v>
+        <v>239.5</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,13 +1082,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>61.60795841097712</v>
+        <v>56.96592695882958</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>31.22551767089019</v>
+        <v>20.22331363676109</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.6946751593947006</v>
+        <v>0.260821056043752</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.0427337590565258</v>
+        <v>-0.6200519475969806</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>1229</v>
+        <v>1216</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>聯華</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>636.0743434608405</v>
+        <v>811.5977010293259</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>42.95</v>
+        <v>74.5</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,49 +1135,49 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>58.49690038346895</v>
+        <v>50.9070825951292</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>24.31493742483805</v>
+        <v>24.28226218086127</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.6200689870236663</v>
+        <v>0.7845249346311086</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M13" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.1345505475628858</v>
+        <v>-0.1043479978554549</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>1513</v>
+        <v>1310</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>台苯</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>604.8123839274464</v>
+        <v>800.0705187209481</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>177</v>
+        <v>10.55</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>56.56839622352619</v>
+        <v>68.69089470721265</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>19.42000373279203</v>
+        <v>29.69225637098092</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.2695043604820097</v>
+        <v>1.607051872094816</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>-0.2020547159488863</v>
+        <v>0.1760901167674798</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>1310</v>
+        <v>1312</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>台苯</t>
+          <t>國喬</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>600.0705187209481</v>
+        <v>799.7475156381042</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>10.55</v>
+        <v>14.1</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>68.6908947267893</v>
+        <v>61.60795840468153</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>29.69225640257012</v>
+        <v>31.22551767789845</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1.607051872094816</v>
+        <v>0.6946751593947006</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.1760901167598481</v>
+        <v>0.0427337590756056</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>1342</v>
+        <v>1313</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>八貫</t>
+          <t>聯成</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>595.2124064961549</v>
+        <v>782.164345458837</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>112.5</v>
+        <v>12.45</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>60.3923352742091</v>
+        <v>63.0435639724742</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>43.23315324725041</v>
+        <v>28.76355397694205</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.3914907445160595</v>
+        <v>0.6841016357975924</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1312,11 +1312,11 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>-0.7093348250282849</v>
+        <v>0.1328057537525827</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -1333,7 +1333,7 @@
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>592.5374222339594</v>
+        <v>732.5384427536607</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>54.6</v>
@@ -1347,13 +1347,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>54.97294861166878</v>
+        <v>54.97294856666763</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>23.0484707072307</v>
+        <v>23.04847066664566</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.5414005659955259</v>
+        <v>0.5415735868204814</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.2168336566594064</v>
+        <v>0.2168336567548034</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>1313</v>
+        <v>1203</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>聯成</t>
+          <t>味王</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>582.164345458837</v>
+        <v>731.2034627892846</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>12.45</v>
+        <v>43.5</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>63.04356400738325</v>
+        <v>55.40609966622797</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>28.76355402845254</v>
+        <v>13.71116021723896</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.6841016357975924</v>
+        <v>0.6189231069800802</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.1328057537354112</v>
+        <v>0.0067779837565174</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>1409</v>
+        <v>1513</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>新纖</t>
+          <t>中興電</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>578.4264923381932</v>
+        <v>719.8123839274464</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>26.05</v>
+        <v>177</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,49 +1453,49 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>55.55815098442999</v>
+        <v>56.56839625442621</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>26.53743095513527</v>
+        <v>19.42000373592466</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.4755775320638987</v>
+        <v>0.2695043604820097</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M19" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>-0.396039520067446</v>
+        <v>-0.2020547161397035</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>1423</v>
+        <v>1305</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>利華</t>
+          <t>華夏</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>571.5145015355199</v>
+        <v>719.5158638448509</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>37.2</v>
+        <v>13.1</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>29.32483519982023</v>
+        <v>50.94417095567216</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>35.00118502521139</v>
+        <v>10.8253113976786</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.0437567868896603</v>
+        <v>0.6622601696387613</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>-0.7841643520611701</v>
+        <v>0.0627532718983357</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>1307</v>
+        <v>1102</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>三芳</t>
+          <t>亞泥</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>571.5011425623018</v>
+        <v>710.7135559505348</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>34.3</v>
+        <v>35</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,16 +1559,16 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>48.7769886822804</v>
+        <v>48.94454843849235</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>22.85822582373663</v>
+        <v>19.85113629791728</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.7601673295371899</v>
+        <v>1.325728643118328</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-0.2915889677767846</v>
+        <v>0.0152243577386158</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>1203</v>
+        <v>1304</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>味王</t>
+          <t>台聚</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>571.2034627892846</v>
+        <v>691.2601685097139</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>43.5</v>
+        <v>13.55</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,16 +1612,16 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>55.40609959937358</v>
+        <v>54.78554929706814</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>13.71116010485929</v>
+        <v>13.28748242744513</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.6189231069800802</v>
+        <v>0.6980615576761292</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.0067779838519214</v>
+        <v>0.070686255745449</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>1568</v>
+        <v>1437</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>倉佑</t>
+          <t>勤益控</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>542.2074281695947</v>
+        <v>662.8990288333815</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>37.4</v>
+        <v>30.2</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,16 +1665,16 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>46.11574600046098</v>
+        <v>68.25934599048068</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>36.32157731494146</v>
+        <v>28.3886748445342</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.5481511942307075</v>
+        <v>0.9746052070870982</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>-1.144701710645603</v>
+        <v>0.1005873001675879</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>1563</v>
+        <v>1446</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>巧新</t>
+          <t>宏和</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>534.2655475708641</v>
+        <v>622.5921358875086</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>62.1</v>
+        <v>16.9</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>52.41690717296778</v>
+        <v>61.86999195543168</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>39.38979235595635</v>
+        <v>22.33612680263924</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.330283154761781</v>
+        <v>0.819436301792646</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>-0.9221481577831973</v>
+        <v>-0.0206478728869695</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>1456</v>
+        <v>1227</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>怡華</t>
+          <t>佳格</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>525.8978673630353</v>
+        <v>620.4697817434123</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>14.4</v>
+        <v>29.35</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>52.59693759537891</v>
+        <v>58.88804820706776</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>20.09683347560499</v>
+        <v>20.55529062683249</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.4200857177204435</v>
+        <v>0.3165862242921347</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-0.0523254966682875</v>
+        <v>0.07322564679672069</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>1216</v>
+        <v>1455</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>集盛</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>506.5977010293259</v>
+        <v>619.3267865590753</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>74.5</v>
+        <v>10</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>50.9070825951292</v>
+        <v>62.9946923666617</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>24.28226216469868</v>
+        <v>38.51358627062707</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.7845249346311086</v>
+        <v>1.059576542476452</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-0.1043479978554549</v>
+        <v>-0.0489650610748367</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>1437</v>
+        <v>1414</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>勤益控</t>
+          <t>東和</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>502.8990288333815</v>
+        <v>613.5046069475602</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>30.2</v>
+        <v>18.4</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>68.25934616995087</v>
+        <v>71.17050771038807</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>28.38867473455305</v>
+        <v>22.6131967700155</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.9746052070870982</v>
+        <v>1.028333008446483</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.1005873001485087</v>
+        <v>0.1223691342903378</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>1514</v>
+        <v>1342</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>八貫</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>493.2392044508297</v>
+        <v>595.2124064961549</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>123</v>
+        <v>112.5</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>50.29523703625354</v>
+        <v>60.39233528537621</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>17.84693017909167</v>
+        <v>43.23315325796767</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.278532524939542</v>
+        <v>0.3914907445160595</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-0.6389093580296188</v>
+        <v>-0.7093348248374998</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>1227</v>
+        <v>1465</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>佳格</t>
+          <t>偉全</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>480.4697817434123</v>
+        <v>594.8716119149825</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>29.35</v>
+        <v>12.6</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>58.88804841858651</v>
+        <v>57.59835779543839</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>20.55529074756173</v>
+        <v>13.75536601297603</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.3165862242921347</v>
+        <v>0.886081663507941</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.0732256466727018</v>
+        <v>0.016147219280181</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, cci_momentum</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>1446</v>
+        <v>1110</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>宏和</t>
+          <t>東泥</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>462.5921358875086</v>
+        <v>587.927618289643</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>16.9</v>
+        <v>15.65</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>61.86999181890722</v>
+        <v>57.3381597252182</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>22.33612680284676</v>
+        <v>30.71871901591674</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.819436301792646</v>
+        <v>0.9314685272357776</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-0.0206478728297322</v>
+        <v>-0.0472001347372844</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, williams_r_recovery, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>1443</v>
+        <v>1315</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>立益</t>
+          <t>達新</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>460.3245657810625</v>
+        <v>586.9175254442898</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>26.45</v>
+        <v>62.5</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>50.55917685085616</v>
+        <v>57.88448747028995</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>17.60509617858568</v>
+        <v>10.87549423479708</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.5259711811889154</v>
+        <v>0.5386799928931806</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-0.1976024400332328</v>
+        <v>0.1006868178045646</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>1465</v>
+        <v>1338</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>偉全</t>
+          <t>廣華-KY</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>454.8716119149826</v>
+        <v>579.4380999945562</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>12.6</v>
+        <v>16.9</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>57.59835765692088</v>
+        <v>54.48314925296239</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>13.75536602034594</v>
+        <v>17.27906301420152</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.886081663507941</v>
+        <v>1.315881958971459</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.0161472193278785</v>
+        <v>-0.0444105882872183</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>1455</v>
+        <v>1409</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>集盛</t>
+          <t>新纖</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>449.3267865590753</v>
+        <v>578.4264923381932</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>10</v>
+        <v>26.05</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>62.99469236313373</v>
+        <v>55.55815096639706</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>38.51358624879235</v>
+        <v>26.53743094690753</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>1.059576542476452</v>
+        <v>0.4755775320638987</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-0.0489650610614809</v>
+        <v>-0.396039520029287</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>1110</v>
+        <v>1423</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>東泥</t>
+          <t>利華</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>447.927618289643</v>
+        <v>571.5145015355199</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>15.65</v>
+        <v>37.2</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>57.33815982615334</v>
+        <v>29.32483519982023</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>30.71871901591674</v>
+        <v>35.00118479716506</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.9314685272357776</v>
+        <v>0.0437567868896603</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-0.0472001347563638</v>
+        <v>-0.7841643518894543</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, williams_r_recovery, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>1315</v>
+        <v>1307</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>達新</t>
+          <t>三芳</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>446.9175254442897</v>
+        <v>571.5011425623018</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>62.5</v>
+        <v>34.3</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>57.8844874294534</v>
+        <v>48.77698858272775</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>10.87549421067279</v>
+        <v>22.85822587749882</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.5386799928931806</v>
+        <v>0.7601673295371899</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.1006868178427183</v>
+        <v>-0.2915889675859904</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>1521</v>
+        <v>1466</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>大億</t>
+          <t>聚隆</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>446.4045857331374</v>
+        <v>564.8922588580555</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>25.6</v>
+        <v>14.8</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>42.92840626671789</v>
+        <v>53.90204751149859</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>15.79541643370335</v>
+        <v>13.17034630081572</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.4443988579723166</v>
+        <v>1.796520407084948</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-0.1502270694262846</v>
+        <v>0.0959982907667228</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>1414</v>
+        <v>1308</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>東和</t>
+          <t>亞聚</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>443.5046069475608</v>
+        <v>562.2907185952171</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>18.4</v>
+        <v>14.1</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,13 +2407,13 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>71.17050776540168</v>
+        <v>54.07070871348311</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>22.61319681395803</v>
+        <v>11.91283585327035</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1.028333008446483</v>
+        <v>0.7673169828156766</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.1223691340941459</v>
+        <v>0.0655497945756566</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>1305</v>
+        <v>1460</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>華夏</t>
+          <t>宏遠</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>439.5158638448509</v>
+        <v>547.5696081881526</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>13.1</v>
+        <v>7.11</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>50.94417107784605</v>
+        <v>50.65427752736539</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>10.82531131795086</v>
+        <v>13.75536731676842</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.6622601696387613</v>
+        <v>0.8624903175193402</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.0627532718029373</v>
+        <v>-0.0139655381144638</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>1338</v>
+        <v>1456</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>廣華-KY</t>
+          <t>怡華</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>439.4380999945562</v>
+        <v>545.8978673630353</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>16.9</v>
+        <v>14.4</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>54.48314919621206</v>
+        <v>52.59693759537891</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>17.27906307803199</v>
+        <v>20.0968333725485</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>1.315881958971459</v>
+        <v>0.4200857177204435</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,11 +2531,11 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-0.0444105883158374</v>
+        <v>-0.0523254966873682</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2552,7 @@
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>434.7361202866857</v>
+        <v>544.7361202866856</v>
       </c>
       <c r="E40" s="2" t="n">
         <v>11.25</v>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>43.41808701968469</v>
+        <v>43.41808706564188</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>24.53594565734221</v>
+        <v>24.5359457114304</v>
       </c>
       <c r="J40" s="2" t="n">
         <v>0.2715082914158829</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-0.0397495299181024</v>
+        <v>-0.0397495299658012</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>1466</v>
+        <v>1438</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>聚隆</t>
+          <t>三地開發</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>424.8922588580613</v>
+        <v>542.5418677632081</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>14.8</v>
+        <v>23</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,16 +2619,16 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>53.90204759032395</v>
+        <v>55.18794917600962</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>13.17034629371711</v>
+        <v>22.79626405806459</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>1.796520407084948</v>
+        <v>0.0866603698696321</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0.0959982907285645</v>
+        <v>0.1987509270319358</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>1402</v>
+        <v>1568</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>遠東新</t>
+          <t>倉佑</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>419.4494093491203</v>
+        <v>542.2074281695947</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>28.5</v>
+        <v>37.4</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>57.0818228173022</v>
+        <v>46.11574602646327</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>18.51765694174517</v>
+        <v>36.32157726020949</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.5302597933203167</v>
+        <v>0.5481511942307075</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.0357470304641005</v>
+        <v>-1.144701710655142</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>1215</v>
+        <v>1402</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>遠東新</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>412.9528349550189</v>
+        <v>534.4494093491203</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>113.5</v>
+        <v>28.5</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>32.74886184628559</v>
+        <v>57.08182280395179</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>44.14845720262405</v>
+        <v>18.51765693074921</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.5404754143860154</v>
+        <v>0.5302597933203167</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.6237311131153431</v>
+        <v>0.0357470303591662</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>1102</v>
+        <v>1563</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>亞泥</t>
+          <t>巧新</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>410.5175513955838</v>
+        <v>534.2655475708641</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>35</v>
+        <v>62.1</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>48.94454853498196</v>
+        <v>52.41690717514241</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>19.85113627531591</v>
+        <v>39.38979244098167</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>1.300473926853394</v>
+        <v>0.330283154761781</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.0152243577290747</v>
+        <v>-0.9221481577450344</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>1236</v>
+        <v>1321</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>宏亞</t>
+          <t>大洋</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>409.0107933156445</v>
+        <v>531.2712271368575</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>25.75</v>
+        <v>30.95</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>59.40009075736552</v>
+        <v>53.26658681801182</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>12.77159557330912</v>
+        <v>33.96280506465359</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.8627202469287483</v>
+        <v>0.4677247048365162</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.0183967633214759</v>
+        <v>0.0042772013976488</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>1531</v>
+        <v>1477</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>高林股</t>
+          <t>聚陽</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>403.1598831556798</v>
+        <v>528.5307397245185</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>12.9</v>
+        <v>219</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>54.61721892762456</v>
+        <v>48.49840321476749</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>15.25184927966821</v>
+        <v>21.74540003787535</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>1.124173193300538</v>
+        <v>0.7243916666100294</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-0.0081874135670221</v>
+        <v>-0.0185515577042085</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>1532</v>
+        <v>1512</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>勤美</t>
+          <t>瑞利</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>402.4421312412183</v>
+        <v>527.3715150447329</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>22.7</v>
+        <v>6.78</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>52.55390072766671</v>
+        <v>44.4052974181108</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>31.78638046268657</v>
+        <v>9.139757906859506</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.4463337734519976</v>
+        <v>0.7947151439342213</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-0.1385734571559507</v>
+        <v>-0.0111722602416573</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>1304</v>
+        <v>1236</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>台聚</t>
+          <t>宏亞</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>401.260168509714</v>
+        <v>524.0107933156445</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>13.55</v>
+        <v>25.75</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>54.78554935024457</v>
+        <v>59.40009059132779</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>13.28748244115987</v>
+        <v>12.7715956381047</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.6980615576761292</v>
+        <v>0.8627202469287483</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.0706862557168287</v>
+        <v>0.0183967633119352</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>1530</v>
+        <v>1463</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>亞崴</t>
+          <t>強盛新</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>396.0919651590343</v>
+        <v>520.3243932502512</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>28.25</v>
+        <v>17.4</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>36.80389437721153</v>
+        <v>39.91325302676221</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>20.56908507598842</v>
+        <v>25.94112774697198</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.308779809005977</v>
+        <v>0.6156375925545289</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-0.4557005933391332</v>
+        <v>-0.014248712801152</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>1319</v>
+        <v>1436</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>東陽</t>
+          <t>華友聯</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>393.6729004558612</v>
+        <v>520.0773484612912</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>77.40000000000001</v>
+        <v>44.85</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>37.3162241607339</v>
+        <v>41.99641484486765</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>31.79072468584416</v>
+        <v>20.65120089423237</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.4158138650592146</v>
+        <v>0.3932463277064868</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-3.097117072307706</v>
+        <v>-0.0044625710891594</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>1308</v>
+        <v>1531</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>亞聚</t>
+          <t>高林股</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>392.2907185952171</v>
+        <v>518.1598831556798</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>14.1</v>
+        <v>12.9</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>54.07070881356121</v>
+        <v>54.61721886303829</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>11.912835833698</v>
+        <v>15.25184921496809</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.7673169828156766</v>
+        <v>1.124173193300538</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.0655497945756566</v>
+        <v>-0.0081874135670221</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>車王電</t>
+          <t>勤美</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>391.6687259915607</v>
+        <v>517.4421312412184</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>36</v>
+        <v>22.7</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>43.65636306171466</v>
+        <v>52.55390091748465</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>34.44406292740273</v>
+        <v>31.78638046268656</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.2624934149575832</v>
+        <v>0.4463337734519976</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-0.4779358435973637</v>
+        <v>-0.13857345716549</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>1321</v>
+        <v>1451</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>大洋</t>
+          <t>年興</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>391.2712271368575</v>
+        <v>516.3860496969222</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>30.95</v>
+        <v>17.1</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>53.26658676936139</v>
+        <v>58.21946263987203</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>33.96280505429343</v>
+        <v>13.82691093066948</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.4677247048365162</v>
+        <v>0.4690367105193788</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.0042772013785684</v>
+        <v>0.0518316921840125</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>1477</v>
+        <v>1535</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>聚陽</t>
+          <t>中宇</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>388.5307397245186</v>
+        <v>511.6980548091277</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>219</v>
+        <v>50.3</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>48.49840329904308</v>
+        <v>52.61854374969417</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>21.74539995334183</v>
+        <v>26.43071564872896</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.7243916666100294</v>
+        <v>0.3577911204517309</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-0.0185515598983553</v>
+        <v>0.0104941299171707</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>1460</v>
+        <v>1309</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>宏遠</t>
+          <t>台達化</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>387.5696081881526</v>
+        <v>511.4262069336658</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>7.11</v>
+        <v>14.7</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>50.65427758824114</v>
+        <v>43.6687359460448</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>13.75536714675356</v>
+        <v>13.13195238451989</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.8624903175193402</v>
+        <v>0.4378179294474449</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-0.0139655381316344</v>
+        <v>0.0512309636933311</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>1436</v>
+        <v>1339</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>華友聯</t>
+          <t>昭輝</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>385.0773484612912</v>
+        <v>508.3404410756954</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>44.85</v>
+        <v>44</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>41.99641435079023</v>
+        <v>54.1399566684706</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>20.65120101901958</v>
+        <v>18.45810721661934</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.3932463277064868</v>
+        <v>0.3981357354485572</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-0.0044625702305823</v>
+        <v>-0.1594018700908782</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>1472</v>
+        <v>1533</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>三洋實業</t>
+          <t>車王電</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>383.8536326050864</v>
+        <v>506.6687259915607</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>88.8</v>
+        <v>36</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>49.59318267122809</v>
+        <v>43.65636305134319</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>8.835280939224798</v>
+        <v>34.44406298973708</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.237736716193269</v>
+        <v>0.2624934149575832</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-0.06557251325460869</v>
+        <v>-0.477935843616439</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>1463</v>
+        <v>1445</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>強盛新</t>
+          <t>大宇</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>380.324393250251</v>
+        <v>503.8641072999519</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>17.4</v>
+        <v>11.4</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>39.91325271986465</v>
+        <v>51.13516156665306</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>25.94112774509676</v>
+        <v>22.95664076228553</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.6156375925545289</v>
+        <v>3.10380488314594</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-0.014248712734375</v>
+        <v>0.085801078928185</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>volume_break, market_above_ma60, adx_trending, stronger_than_market, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>1451</v>
+        <v>1472</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>年興</t>
+          <t>三洋實業</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>376.3860496969223</v>
+        <v>498.8536326050864</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>17.1</v>
+        <v>88.8</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>58.2194624662589</v>
+        <v>49.59318264335251</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>13.8269109156239</v>
+        <v>8.835280977435669</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.4690367105193788</v>
+        <v>0.237736716193269</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.0518316921553921</v>
+        <v>-0.0655725130065785</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>1522</v>
+        <v>1319</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>堤維西</t>
+          <t>東陽</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>373.1475076320209</v>
+        <v>488.6729004558612</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>30.45</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>45.84100702133805</v>
+        <v>37.3162242185729</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>15.31239852845251</v>
+        <v>31.7907246923895</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.6253941128165941</v>
+        <v>0.4158138650592146</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-0.1187632086500735</v>
+        <v>-3.097117072593887</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>1341</v>
+        <v>1522</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>富林-KY</t>
+          <t>堤維西</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>372.674228218146</v>
+        <v>488.1475076320209</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>57.7</v>
+        <v>30.45</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>33.29132192029662</v>
+        <v>45.84100704709366</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>21.71527501592693</v>
+        <v>15.31239861623724</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.7265261958589655</v>
+        <v>0.6253941128165941</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-0.59937359976567</v>
+        <v>-0.1187632084306606</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>1535</v>
+        <v>1443</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>中宇</t>
+          <t>立益</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>371.6980548091278</v>
+        <v>480.3245657810625</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>50.3</v>
+        <v>26.45</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,16 +3732,16 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>52.61854380112924</v>
+        <v>50.55917685085616</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>26.43071563775664</v>
+        <v>17.60509609253299</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.3577911204517309</v>
+        <v>0.5259711811889154</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.0104941298408529</v>
+        <v>-0.1976024400141533</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>1339</v>
+        <v>1514</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>昭輝</t>
+          <t>亞力</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>368.3404410756954</v>
+        <v>478.2392044508297</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>44</v>
+        <v>123</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>54.13995647138656</v>
+        <v>50.29523707551255</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>18.45810720746173</v>
+        <v>17.84693013411956</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.3981357354485572</v>
+        <v>0.278532524939542</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-0.1594018698237688</v>
+        <v>-0.6389093585066132</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>1225</v>
+        <v>1201</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>福懋油</t>
+          <t>味全</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>367.4882864371002</v>
+        <v>456.2508689484777</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>29.15</v>
+        <v>12.3</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>42.16004964826482</v>
+        <v>46.59987525013683</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>16.12373538821999</v>
+        <v>18.06690558847577</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.6482804591163699</v>
+        <v>0.6913200608131235</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.1718647623666548</v>
+        <v>-0.0061439909614337</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>1438</v>
+        <v>1521</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>三地開發</t>
+          <t>大億</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>352.5418677632081</v>
+        <v>446.4045857331374</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>23</v>
+        <v>25.6</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>55.1879489569388</v>
+        <v>42.92840628526548</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>22.79626430967394</v>
+        <v>15.79541635073135</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.0866603698696321</v>
+        <v>0.4443988579723166</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.1987509274516837</v>
+        <v>-0.1502270693785881</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>1504</v>
+        <v>1233</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>東元</t>
+          <t>天仁</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>350.2658908381316</v>
+        <v>440.012199645946</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>70.09999999999999</v>
+        <v>28.1</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,16 +3944,16 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>47.71516235955903</v>
+        <v>49.31989836401813</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>15.55457829847366</v>
+        <v>13.19881145540768</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.1915637755825163</v>
+        <v>0.5241662318366336</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-0.5128307330796059</v>
+        <v>0.0771623866407031</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>1201</v>
+        <v>1323</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>味全</t>
+          <t>永裕</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>341.2508689484777</v>
+        <v>439.4737827730961</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>12.3</v>
+        <v>19.7</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>46.59987517775146</v>
+        <v>46.39693353110336</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>18.06690554126784</v>
+        <v>15.21133788097554</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.6913200608131235</v>
+        <v>0.2555846322342849</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-0.0061439909137369</v>
+        <v>-0.0100162670541008</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>1445</v>
+        <v>1537</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>大宇</t>
+          <t>廣隆</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>333.8641072999519</v>
+        <v>422.562087277832</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>11.4</v>
+        <v>125.5</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>51.13516161369113</v>
+        <v>46.73397330394009</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>22.95664072419768</v>
+        <v>16.9734032010927</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>3.10380488314594</v>
+        <v>0.5484847494655077</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.0858010788995672</v>
+        <v>-0.2917680524869053</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, adx_trending, cci_momentum, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>1323</v>
+        <v>1215</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>永裕</t>
+          <t>卜蜂</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>324.4737827730961</v>
+        <v>412.9528349550189</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>19.7</v>
+        <v>113.5</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>46.39693350585169</v>
+        <v>32.74886178232218</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>15.21133797799115</v>
+        <v>44.14845716493449</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.2555846322342849</v>
+        <v>0.5404754143860154</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.0100162670445617</v>
+        <v>0.6237311135923367</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>1538</v>
+        <v>1232</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>正峰</t>
+          <t>大統益</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>307.5608673263868</v>
+        <v>412.595314669338</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>11.2</v>
+        <v>141.5</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>51.34446950082626</v>
+        <v>32.83878530209448</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>5.932183151100316</v>
+        <v>37.23472216669028</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.3041056542982849</v>
+        <v>0.6595314669337973</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-0.2091233916437913</v>
+        <v>-0.4634766156668171</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>1232</v>
+        <v>1256</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>大統益</t>
+          <t>鮮活果汁-KY</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>297.595314669338</v>
+        <v>410.9070033440218</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>141.5</v>
+        <v>179.5</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>32.83878542690394</v>
+        <v>48.24081807851016</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>37.2347222337463</v>
+        <v>15.35140973073198</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.6595314669337973</v>
+        <v>2.17663214968868</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.4634766159530024</v>
+        <v>-0.8713752043773729</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>1470</v>
+        <v>1417</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>大統新創</t>
+          <t>嘉裕</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>297.2806227383608</v>
+        <v>402.7439347785058</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>21.3</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>51.68387400121714</v>
+        <v>54.81971694158998</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>10.36276488554193</v>
+        <v>16.37619126302566</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.6375137722730899</v>
+        <v>1.301175473306529</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.6672208782956139</v>
+        <v>0.0092043650501719</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>1256</v>
+        <v>1475</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>鮮活果汁-KY</t>
+          <t>業旺</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>295.9070033440218</v>
+        <v>402.1770922686154</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>179.5</v>
+        <v>26.85</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,16 +4315,16 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>48.24081806115485</v>
+        <v>50.40023379731875</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>15.35140984352315</v>
+        <v>18.07426881691683</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>2.17663214968868</v>
+        <v>0.2758668714688036</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.8713752048543665</v>
+        <v>0.0491172492568872</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>1537</v>
+        <v>1440</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>廣隆</t>
+          <t>南紡</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>287.5620872778319</v>
+        <v>401.7222342343</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>125.5</v>
+        <v>13.35</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>46.73397302379992</v>
+        <v>53.31545039120245</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>16.97340318731147</v>
+        <v>19.83214462903099</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.5484847494655077</v>
+        <v>0.3849150099561772</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-0.2917680522007176</v>
+        <v>-0.0543387535361207</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>1432</v>
+        <v>1471</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>大魯閣</t>
+          <t>首利</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>286.4886336488139</v>
+        <v>398.4357964765153</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>15.25</v>
+        <v>10.8</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,16 +4421,16 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>30.33743849993996</v>
+        <v>47.32927341356859</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>29.70049908160862</v>
+        <v>12.05468740179515</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.3528102658149818</v>
+        <v>0.4878092981210755</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-0.2502435665882045</v>
+        <v>-0.0313872327687071</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>1471</v>
+        <v>1454</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>首利</t>
+          <t>台富</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>283.4357964765153</v>
+        <v>396.1038448105663</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>10.8</v>
+        <v>12.75</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,16 +4474,16 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>47.32927335419824</v>
+        <v>45.66235172224758</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>12.05468738927283</v>
+        <v>16.94041470511916</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.4878092981210755</v>
+        <v>0.3291159520505754</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.0313872327496275</v>
+        <v>-0.0034873576878705</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>1512</v>
+        <v>1530</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>瑞利</t>
+          <t>亞崴</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>277.3715150447327</v>
+        <v>396.0919651590343</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>6.78</v>
+        <v>28.25</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,16 +4527,16 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>44.40529721376955</v>
+        <v>36.80389440397808</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>9.139757890070928</v>
+        <v>20.56908503318612</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.7947151439342213</v>
+        <v>0.308779809005977</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.0111722602531046</v>
+        <v>-0.4557005933009745</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>1419</v>
+        <v>1225</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>新紡</t>
+          <t>福懋油</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>270.3668283787216</v>
+        <v>387.4882864371002</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>65</v>
+        <v>29.15</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>47.21278366019464</v>
+        <v>42.16004964826482</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>16.61741026073522</v>
+        <v>16.12373538821999</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>1.181820664791194</v>
+        <v>0.6482804591163699</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.2098552654880203</v>
+        <v>-0.1718647623666548</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>1475</v>
+        <v>1439</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>業旺</t>
+          <t>雋揚</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>267.1770922686154</v>
+        <v>384.5085604045846</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>26.85</v>
+        <v>24.2</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,16 +4633,16 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>50.40023363369383</v>
+        <v>44.77033175672811</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>18.07426878924248</v>
+        <v>9.221585074733211</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.2758668714688036</v>
+        <v>0.8252128899544234</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.0491172492568872</v>
+        <v>-0.079363803084399</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>1440</v>
+        <v>1341</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>南紡</t>
+          <t>富林-KY</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>266.7222342342998</v>
+        <v>372.6742282181459</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>13.35</v>
+        <v>57.7</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>53.31545044179892</v>
+        <v>33.29132191000392</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>19.83214437829402</v>
+        <v>21.71527501879977</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.3849150099561772</v>
+        <v>0.7265261958589655</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-0.0543387535551998</v>
+        <v>-0.5993735996702729</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>1516</v>
+        <v>1504</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>川飛</t>
+          <t>東元</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>261.6821797167188</v>
+        <v>370.2658908381316</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>19.3</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,49 +4739,49 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>36.35147705348203</v>
+        <v>47.71516235706697</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>25.29469147526968</v>
+        <v>15.55457828911673</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.2391874499531545</v>
+        <v>0.1915637755825163</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L81" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M81" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-0.1697064490021215</v>
+        <v>-0.5128307330605225</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>1309</v>
+        <v>1316</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>台達化</t>
+          <t>上曜</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>261.4262069336658</v>
+        <v>365.546820646669</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>14.7</v>
+        <v>10.45</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,16 +4792,16 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>43.66873594094868</v>
+        <v>46.25842686502303</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>13.13195236689072</v>
+        <v>14.83553692173626</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.4378179294474449</v>
+        <v>0.3910205908515829</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.0512309637124095</v>
+        <v>-0.0241153739299033</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>1454</v>
+        <v>1524</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>台富</t>
+          <t>耿鼎</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>261.1038448105664</v>
+        <v>355.7213453981487</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>12.75</v>
+        <v>28.95</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,16 +4845,16 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>45.66235174131055</v>
+        <v>43.82619362915029</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>16.94041470557653</v>
+        <v>15.71339439746109</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.3291159520505754</v>
+        <v>0.2555636655570108</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-0.0034873576974099</v>
+        <v>-0.2087652784236621</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>1439</v>
+        <v>1213</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>雋揚</t>
+          <t>大飲</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>249.5085604045846</v>
+        <v>354.5940522182417</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>24.2</v>
+        <v>8.19</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>44.77033175158202</v>
+        <v>51.27171315492384</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>9.221585173576701</v>
+        <v>8.390557504539235</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.8252128899544234</v>
+        <v>1.129469688563635</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-0.0793638031034796</v>
+        <v>0.1157805368514265</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>1417</v>
+        <v>1108</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>嘉裕</t>
+          <t>幸福</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>242.7439347785058</v>
+        <v>351.0681433427822</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>8.529999999999999</v>
+        <v>13.8</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,16 +4951,16 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>54.81971697023915</v>
+        <v>47.36037134835879</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>16.37619127906488</v>
+        <v>24.27368505319816</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>1.301175473306529</v>
+        <v>0.4694586994923722</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>0.0092043650387236</v>
+        <v>0.0146859695623309</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, cci_momentum, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>1104</v>
+        <v>1101</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>環泥</t>
+          <t>台泥</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>242.3806641691428</v>
+        <v>350.8807718459816</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>26.8</v>
+        <v>24.05</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>31.54877397791263</v>
+        <v>45.07608866361486</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>32.48219219157779</v>
+        <v>14.75481523083051</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>1.031491981906816</v>
+        <v>1.102107121372954</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.2763328686936542</v>
+        <v>-0.0267016449482944</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>1108</v>
+        <v>1526</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>幸福</t>
+          <t>日馳</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>236.0681433427822</v>
+        <v>339.8832978302631</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>13.8</v>
+        <v>14.25</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>47.36037125666306</v>
+        <v>41.82321718594245</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>24.27368503971093</v>
+        <v>23.01783197408957</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.4694586994923722</v>
+        <v>0.4021282730769997</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.0146859695814104</v>
+        <v>-0.0049705376162781</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>1101</v>
+        <v>1474</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>台泥</t>
+          <t>弘裕</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>235.8807718459816</v>
+        <v>338.4356360736296</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>24.05</v>
+        <v>10.15</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,16 +5110,16 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>45.07608879934919</v>
+        <v>51.49188997241881</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>14.75481517219794</v>
+        <v>22.29120390734113</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>1.102107121372954</v>
+        <v>0.8864992123156838</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.026701645005534</v>
+        <v>-0.0113622340807784</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>1519</v>
+        <v>1506</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>正道</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>231.114673207624</v>
+        <v>337.2376377542076</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>776</v>
+        <v>9.99</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>41.21338800634899</v>
+        <v>41.71411365900792</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>11.2794399605724</v>
+        <v>24.85367786857468</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.6951657138127181</v>
+        <v>0.7263140694343684</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-2.403428962048128</v>
+        <v>-0.0114759390197451</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>1526</v>
+        <v>1219</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>日馳</t>
+          <t>福壽</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>224.8832978302627</v>
+        <v>335.1879282143825</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>14.25</v>
+        <v>12.5</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>41.82321659149864</v>
+        <v>44.16080626572369</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>23.01783198270029</v>
+        <v>26.30556479545517</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.4021282730769997</v>
+        <v>0.5828863543369061</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-0.0049705376258172</v>
+        <v>0.0230388084284247</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>1506</v>
+        <v>1529</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>正道</t>
+          <t>樂事綠能</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>222.2376377542076</v>
+        <v>333.3680594784605</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>9.99</v>
+        <v>22.6</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,16 +5269,16 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>41.71411363439206</v>
+        <v>50.55460525808085</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>24.85367786857468</v>
+        <v>13.55173946549843</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.7263140694343684</v>
+        <v>0.4466383564906953</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-0.0114759390292855</v>
+        <v>-0.0807387190253573</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>1524</v>
+        <v>1416</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>耿鼎</t>
+          <t>廣豐</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>220.7213453981488</v>
+        <v>330.966794641985</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>28.95</v>
+        <v>10.85</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>43.8261935659102</v>
+        <v>40.95183571303514</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>15.71339441586378</v>
+        <v>25.05907340311243</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.2555636655570108</v>
+        <v>0.3075153853976668</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.2087652783187286</v>
+        <v>-0.0337870989207116</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>1416</v>
+        <v>1517</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>廣豐</t>
+          <t>利奇</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>215.966794641985</v>
+        <v>328.2051916790675</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>10.85</v>
+        <v>10.45</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>40.95183569257049</v>
+        <v>52.2810783443973</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>25.05907348773124</v>
+        <v>19.37544274972132</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.3075153853976668</v>
+        <v>0.9153247802306972</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.033787098901632</v>
+        <v>0.0044073950515462</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>1316</v>
+        <v>1473</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>上曜</t>
+          <t>台南</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>215.5468206466689</v>
+        <v>327.2543941287604</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>10.45</v>
+        <v>19.7</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>46.25842667496739</v>
+        <v>33.01912578478657</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>14.83553695782357</v>
+        <v>20.63761794642405</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.3910205908515829</v>
+        <v>1.199027706165227</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.0241153737868094</v>
+        <v>-0.0411046438621563</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>1233</v>
+        <v>1527</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>天仁</t>
+          <t>鑽全</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>215.0121996459463</v>
+        <v>315.3249805632175</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>28.1</v>
+        <v>33.2</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>49.31989837814663</v>
+        <v>50.71329739428844</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>13.19881141803624</v>
+        <v>15.96153331853252</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.5241662318366336</v>
+        <v>0.8998487259832364</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.0771623866597828</v>
+        <v>-0.0230555039577532</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>1213</v>
+        <v>1476</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>大飲</t>
+          <t>儒鴻</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>214.5940522182417</v>
+        <v>313.0578507535686</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>8.19</v>
+        <v>312.5</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>51.2717131448556</v>
+        <v>38.75710717061613</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>8.390557497940133</v>
+        <v>18.78236483565287</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>1.129469688563635</v>
+        <v>0.9929040796963278</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.1157805368323472</v>
+        <v>-2.230398294668328</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>1517</v>
+        <v>1218</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>利奇</t>
+          <t>泰山</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>213.2051916790675</v>
+        <v>308.5071114385674</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>10.45</v>
+        <v>17.85</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>52.2810783443973</v>
+        <v>36.54639550622965</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>19.37544257966229</v>
+        <v>32.03256096377736</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.9153247802306972</v>
+        <v>0.4802478491525077</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.0044073950229271</v>
+        <v>-0.0499385367168905</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>1473</v>
+        <v>1410</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>台南</t>
+          <t>南染</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>212.2543941287604</v>
+        <v>307.6089577420435</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>19.7</v>
+        <v>24.8</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>33.01912558706583</v>
+        <v>39.92536183376981</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>20.63761791051603</v>
+        <v>15.28207345109904</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>1.199027706165227</v>
+        <v>1.463473946179756</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.0411046438621563</v>
+        <v>0.1403413578960646</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>1582</v>
+        <v>1538</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>信錦</t>
+          <t>正峰</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>210.0470706512753</v>
+        <v>307.5608673263869</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>83.40000000000001</v>
+        <v>11.2</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>35.49467673140981</v>
+        <v>51.34446950643154</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>19.89083295996802</v>
+        <v>5.932183155742026</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.269026386860885</v>
+        <v>0.3041056542982849</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-1.266256160442596</v>
+        <v>-0.2091233917296496</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>1536</v>
+        <v>1220</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>和大</t>
+          <t>台榮</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>206.8870400652972</v>
+        <v>307.2601285402018</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>47.7</v>
+        <v>11.5</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>42.53309888617298</v>
+        <v>31.148947086495</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>10.80031931552593</v>
+        <v>32.64339054580765</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.4227647583749483</v>
+        <v>0.8766769975423692</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-0.157025750043396</v>
+        <v>-0.0024303404275667</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>1474</v>
+        <v>1103</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>弘裕</t>
+          <t>嘉泥</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>203.4356360736296</v>
+        <v>306.6541162603082</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>10.15</v>
+        <v>13.4</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>51.49189007337292</v>
+        <v>45.69234994821385</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>22.29120353218689</v>
+        <v>12.22618125421024</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.8864992123156838</v>
+        <v>0.7084516273488518</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-0.0113622341189375</v>
+        <v>-0.0285927846981333</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>1529</v>
+        <v>1540</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>樂事綠能</t>
+          <t>喬福</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>198.3680594784607</v>
+        <v>304.1925307028255</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>22.6</v>
+        <v>21.7</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,16 +5852,16 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>50.55460516332095</v>
+        <v>49.64331082527502</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>13.55173946211427</v>
+        <v>12.22278483185475</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.4466383564906953</v>
+        <v>0.2875133158643016</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.0807387189490382</v>
+        <v>-0.07520190372499549</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>1476</v>
+        <v>1109</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>儒鴻</t>
+          <t>信大</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>198.0578507535686</v>
+        <v>298.468235885365</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>312.5</v>
+        <v>14.55</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>38.75710707649529</v>
+        <v>42.80169251336103</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>18.78236482714232</v>
+        <v>20.19651717744249</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.9929040796963278</v>
+        <v>0.997713677332238</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-2.230398295049889</v>
+        <v>0.0117052407263962</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>1219</v>
+        <v>1470</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>福壽</t>
+          <t>大統新創</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>195.1879282143825</v>
+        <v>297.2806227383608</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>12.5</v>
+        <v>21.3</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>44.16080638866649</v>
+        <v>51.6838739936554</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>26.30556476915189</v>
+        <v>10.36276484132874</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.5828863543369061</v>
+        <v>0.6375137722730899</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.0230388084284247</v>
+        <v>0.6672208783433147</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>1218</v>
+        <v>1432</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>泰山</t>
+          <t>大魯閣</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>193.5071114385674</v>
+        <v>286.488633648814</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>17.85</v>
+        <v>15.25</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>36.5463956342255</v>
+        <v>30.3374385685285</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>32.03256088616802</v>
+        <v>29.70049908204482</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.4802478491525077</v>
+        <v>0.3528102658149818</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.0499385367645869</v>
+        <v>-0.2502435665786641</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>1220</v>
+        <v>1541</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>台榮</t>
+          <t>錩泰</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>192.2601285402018</v>
+        <v>280.4328930574536</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>11.5</v>
+        <v>21.45</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>31.14894722009593</v>
+        <v>46.61220640387052</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>32.64339056388962</v>
+        <v>11.95565957341016</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.8766769975423692</v>
+        <v>0.8385483787824115</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.0024303404371057</v>
+        <v>0.0651501323819417</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>1103</v>
+        <v>1539</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>嘉泥</t>
+          <t>巨庭</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>191.6541162603082</v>
+        <v>278.4910203393775</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>13.4</v>
+        <v>15.65</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,16 +6117,16 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>45.69235010834402</v>
+        <v>46.144089823638</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>12.22618119816194</v>
+        <v>15.24910684366293</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.7084516273488518</v>
+        <v>0.689225510691218</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.0285927847172122</v>
+        <v>-0.0211089757256787</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>1325</v>
+        <v>1413</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>恆大</t>
+          <t>宏洲</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>179.7097559915181</v>
+        <v>273.3757221026866</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>24.2</v>
+        <v>9.35</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,16 +6170,16 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>29.13267399827636</v>
+        <v>47.60153386285965</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>21.80621020549733</v>
+        <v>14.72261048812084</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.3288852007819675</v>
+        <v>0.5526834947385759</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.2095539948812054</v>
+        <v>-0.0174515505625352</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>1528</v>
+        <v>1419</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>恩德</t>
+          <t>新紡</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>176.9662681451303</v>
+        <v>270.3668283787226</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>23.55</v>
+        <v>65</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>38.60093436659866</v>
+        <v>47.21278368589092</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>9.124798198107795</v>
+        <v>16.61741026986856</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.235867549761436</v>
+        <v>1.181820664791194</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.2573652308542477</v>
+        <v>-0.2098552655548038</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>1527</v>
+        <v>1452</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>鑽全</t>
+          <t>宏益</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>175.3249805632173</v>
+        <v>264.9099496057992</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>33.2</v>
+        <v>10.95</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>50.71329721927829</v>
+        <v>50.73143478649987</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>15.96153331554387</v>
+        <v>15.94394985799878</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.8998487259832364</v>
+        <v>1.169847836508585</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.0230555038814361</v>
+        <v>0.007826362196622701</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>1540</v>
+        <v>1217</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>喬福</t>
+          <t>愛之味</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>169.1925307028255</v>
+        <v>262.1559075551302</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>21.7</v>
+        <v>9.82</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>49.64331067624396</v>
+        <v>49.86013526869248</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>12.22278479526329</v>
+        <v>17.0686175404558</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.2875133158643016</v>
+        <v>0.4156410394700787</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.0752019036582169</v>
+        <v>-0.0071556975756895</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>1410</v>
+        <v>1516</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>南染</t>
+          <t>川飛</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>167.6089577420435</v>
+        <v>261.6821797167188</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>24.8</v>
+        <v>19.3</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>39.92536158379432</v>
+        <v>36.35147733380131</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>15.28207347325296</v>
+        <v>25.29469149037793</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>1.463473946179756</v>
+        <v>0.2391874499531545</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.1403413580486983</v>
+        <v>-0.1697064490307386</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>1541</v>
+        <v>1418</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>錩泰</t>
+          <t>東華</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>165.4328930574536</v>
+        <v>259.5368718334296</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>21.45</v>
+        <v>17.8</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,16 +6435,16 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>46.61220637343697</v>
+        <v>40.64808435946832</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>11.95565957341016</v>
+        <v>16.44474225329314</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.8385483787824115</v>
+        <v>0.5483856498219236</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>0.0651501324010224</v>
+        <v>-0.0822992920196233</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>1340</v>
+        <v>1442</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>勝悅-KY</t>
+          <t>名軒</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>162.2716689982169</v>
+        <v>254.8045513705129</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>5.3</v>
+        <v>26.9</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>36.61509562186978</v>
+        <v>47.39582284743685</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>15.73289388709003</v>
+        <v>17.54993041865468</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.4166546568033191</v>
+        <v>0.2073559110408096</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.036228294152262</v>
+        <v>-0.0839404098832249</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>1109</v>
+        <v>1441</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>信大</t>
+          <t>大東</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>158.468235885365</v>
+        <v>253.585072319278</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>14.55</v>
+        <v>9</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,16 +6541,16 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>42.8016928415373</v>
+        <v>37.2144271448609</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>20.19651695726259</v>
+        <v>18.25534701923331</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.997713677332238</v>
+        <v>1.366770329405967</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>0.0117052407073166</v>
+        <v>0.0113464876928801</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>1452</v>
+        <v>1231</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>宏益</t>
+          <t>聯華食</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>149.9099496057992</v>
+        <v>246.62412184289</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>10.95</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>50.73143481483687</v>
+        <v>48.89259974591932</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>15.94394981952147</v>
+        <v>18.85583376365528</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>1.169847836508585</v>
+        <v>1.038839937540629</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>0.0078263621870832</v>
+        <v>0.0191144702179165</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>1217</v>
+        <v>1558</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>愛之味</t>
+          <t>伸興</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>147.1559075551303</v>
+        <v>246.5862576804784</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>9.82</v>
+        <v>90.5</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,16 +6647,16 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>49.86013510044631</v>
+        <v>46.15581409627772</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>17.0686175404558</v>
+        <v>10.37978637722944</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.4156410394700787</v>
+        <v>0.7428301990533014</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-0.0071556975470701</v>
+        <v>-0.0288353611342065</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>1418</v>
+        <v>1464</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>東華</t>
+          <t>得力</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>144.5368718334296</v>
+        <v>243.3354596956525</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>17.8</v>
+        <v>10.25</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,13 +6700,13 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>40.64808413288856</v>
+        <v>49.2567993700944</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>16.44474216792589</v>
+        <v>15.14059230155944</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.5483856498219236</v>
+        <v>0.5449197495836746</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>-0.08229929195284651</v>
+        <v>-0.0171495156996195</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>1539</v>
+        <v>1459</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>巨庭</t>
+          <t>聯發</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>143.4910203393776</v>
+        <v>242.9767030299901</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>15.65</v>
+        <v>11.75</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,16 +6753,16 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>46.14408977034135</v>
+        <v>51.31541696536959</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>15.24910682363298</v>
+        <v>15.21620685510797</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.689225510691218</v>
+        <v>0.6167117179379266</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-0.0211089757256787</v>
+        <v>-0.0067369354086268</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>1442</v>
+        <v>1104</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>名軒</t>
+          <t>環泥</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>139.8045513705129</v>
+        <v>242.3806641691428</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>26.9</v>
+        <v>26.8</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,13 +6806,13 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>47.39582270738768</v>
+        <v>31.54877406452785</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>17.54993043441044</v>
+        <v>32.48219225560186</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.2073559110408096</v>
+        <v>1.031491981906816</v>
       </c>
       <c r="K120" s="2" t="n">
         <v>0</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>-0.0839404096351916</v>
+        <v>-0.276332868684116</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>1413</v>
+        <v>1519</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>宏洲</t>
+          <t>華城</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>138.3757221026866</v>
+        <v>231.1223144365636</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>9.35</v>
+        <v>776</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,13 +6859,13 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>47.60153383963711</v>
+        <v>41.21338804725782</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>14.72261047841918</v>
+        <v>11.2794399500838</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.5526834947385759</v>
+        <v>0.6963109616410288</v>
       </c>
       <c r="K121" s="2" t="n">
         <v>0</v>
@@ -6877,31 +6877,31 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>-0.0174515505625352</v>
+        <v>-2.403428963192859</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>1231</v>
+        <v>1582</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>聯華食</t>
+          <t>信錦</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>131.6241218428899</v>
+        <v>230.0470706512753</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>87.09999999999999</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,16 +6912,16 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>48.89259974591932</v>
+        <v>35.49467680555757</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>18.85583376365528</v>
+        <v>19.89083299856676</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>1.038839937540629</v>
+        <v>0.269026386860885</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L122" s="2" t="n">
         <v>0</v>
@@ -6930,31 +6930,31 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>0.0191144704087181</v>
+        <v>-1.266256161263015</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>1441</v>
+        <v>1324</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>大東</t>
+          <t>地球</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>118.5850723192779</v>
+        <v>226.0475284152418</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>9</v>
+        <v>10.35</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,13 +6965,13 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>37.21442723037264</v>
+        <v>46.2845201577471</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>18.25534703645419</v>
+        <v>15.37857272208669</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>1.366770329405967</v>
+        <v>0.6804816464961965</v>
       </c>
       <c r="K123" s="2" t="n">
         <v>0</v>
@@ -6983,31 +6983,31 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>0.0113464876928801</v>
+        <v>-0.0130666284811415</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>1558</v>
+        <v>1468</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>伸興</t>
+          <t>昶和</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>111.5862576804784</v>
+        <v>222.7138136086618</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>90.5</v>
+        <v>12</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,16 +7018,16 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>46.15581395812915</v>
+        <v>51.245217826672</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>10.37978637824788</v>
+        <v>8.333596771216998</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.7428301990533014</v>
+        <v>0.984257781049888</v>
       </c>
       <c r="K124" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L124" s="2" t="n">
         <v>0</v>
@@ -7036,31 +7036,31 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>-0.02883536111512</v>
+        <v>0.0111962705717917</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>1569</v>
+        <v>1457</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>濱川</t>
+          <t>宜進</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>111.1541941784346</v>
+        <v>212.8956579184204</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>45.9</v>
+        <v>14.05</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,13 +7071,13 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>36.13744609815215</v>
+        <v>41.81613004451668</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>18.76366787686177</v>
+        <v>13.02469266283945</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.427095637579458</v>
+        <v>0.2951069184268555</v>
       </c>
       <c r="K125" s="2" t="n">
         <v>0</v>
@@ -7089,31 +7089,31 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>-0.2214655011121311</v>
+        <v>-0.0408223301465995</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>1324</v>
+        <v>1536</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>地球</t>
+          <t>和大</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>111.0475284152418</v>
+        <v>206.8870400652973</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>10.35</v>
+        <v>47.7</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -7124,13 +7124,13 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>46.28452026730584</v>
+        <v>42.53309893404159</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>15.3785727220867</v>
+        <v>10.80031932328107</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.6804816464961965</v>
+        <v>0.4227647583749483</v>
       </c>
       <c r="K126" s="2" t="n">
         <v>0</v>
@@ -7142,31 +7142,31 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>-0.0130666284906836</v>
+        <v>-0.1570257501769487</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>1459</v>
+        <v>1528</v>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>聯發</t>
+          <t>恩德</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
         <v/>
       </c>
       <c r="D127" s="2" t="n">
-        <v>107.9767030299901</v>
+        <v>191.9662681451303</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>11.75</v>
+        <v>23.55</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -7177,13 +7177,13 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>51.3154168520004</v>
+        <v>38.60093438733633</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>15.21620679681242</v>
+        <v>9.124798178665282</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>0.6167117179379266</v>
+        <v>0.235867549761436</v>
       </c>
       <c r="K127" s="2" t="n">
         <v>0</v>
@@ -7195,31 +7195,31 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>-0.0067369353704662</v>
+        <v>-0.2573652308733281</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>1464</v>
+        <v>1467</v>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>得力</t>
+          <t>南緯</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
         <v/>
       </c>
       <c r="D128" s="2" t="n">
-        <v>103.3354596956524</v>
+        <v>180.4587529305054</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>10.25</v>
+        <v>7.3</v>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
@@ -7230,13 +7230,13 @@
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>49.25679913236502</v>
+        <v>51.49233093284489</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>15.14059228148835</v>
+        <v>19.48444192754602</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>0.5449197495836746</v>
+        <v>0.753520533507481</v>
       </c>
       <c r="K128" s="2" t="n">
         <v>0</v>
@@ -7248,31 +7248,31 @@
         <v>-1</v>
       </c>
       <c r="N128" s="2" t="n">
-        <v>-0.0171495156233015</v>
+        <v>-0.0354559448044698</v>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>1457</v>
+        <v>1325</v>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>宜進</t>
+          <t>恆大</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
         <v/>
       </c>
       <c r="D129" s="2" t="n">
-        <v>97.8956579184204</v>
+        <v>179.7097559915061</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>14.05</v>
+        <v>24.2</v>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
@@ -7283,13 +7283,13 @@
         <v>0</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>41.81613009322184</v>
+        <v>29.13267392696406</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>13.02469261896312</v>
+        <v>21.8062102697038</v>
       </c>
       <c r="J129" s="2" t="n">
-        <v>0.2951069184268555</v>
+        <v>0.3288852007819675</v>
       </c>
       <c r="K129" s="2" t="n">
         <v>0</v>
@@ -7301,31 +7301,31 @@
         <v>-1</v>
       </c>
       <c r="N129" s="2" t="n">
-        <v>-0.0408223301561387</v>
+        <v>-0.2095539948239694</v>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>1468</v>
+        <v>1340</v>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>昶和</t>
+          <t>勝悅-KY</t>
         </is>
       </c>
       <c r="C130" s="2" t="n">
         <v/>
       </c>
       <c r="D130" s="2" t="n">
-        <v>62.71381360866185</v>
+        <v>162.2716689982168</v>
       </c>
       <c r="E130" s="2" t="n">
-        <v>12</v>
+        <v>5.3</v>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
@@ -7336,13 +7336,13 @@
         <v>0</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>51.24521777067186</v>
+        <v>36.61509563094656</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>8.333596739241424</v>
+        <v>15.73289390656439</v>
       </c>
       <c r="J130" s="2" t="n">
-        <v>0.984257781049888</v>
+        <v>0.4166546568033191</v>
       </c>
       <c r="K130" s="2" t="n">
         <v>0</v>
@@ -7354,31 +7354,31 @@
         <v>-1</v>
       </c>
       <c r="N130" s="2" t="n">
-        <v>0.0111962705622523</v>
+        <v>-0.0362282941579863</v>
       </c>
       <c r="O130" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>1467</v>
+        <v>1569</v>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>南緯</t>
+          <t>濱川</t>
         </is>
       </c>
       <c r="C131" s="2" t="n">
         <v/>
       </c>
       <c r="D131" s="2" t="n">
-        <v>40.45875293050546</v>
+        <v>111.1541941784346</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>7.3</v>
+        <v>45.9</v>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
@@ -7389,16 +7389,16 @@
         <v>0</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>51.49233076490098</v>
+        <v>36.13744614731426</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>19.48444184569508</v>
+        <v>18.76366786552803</v>
       </c>
       <c r="J131" s="2" t="n">
-        <v>0.753520533507481</v>
+        <v>0.427095637579458</v>
       </c>
       <c r="K131" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L131" s="2" t="n">
         <v>0</v>
@@ -7407,7 +7407,7 @@
         <v>-1</v>
       </c>
       <c r="N131" s="2" t="n">
-        <v>-0.0354559447682201</v>
+        <v>-0.2214655011884512</v>
       </c>
       <c r="O131" s="2" t="inlineStr">
         <is>
